--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-23_ppap_sunum_indeksi_psw__parca_sunum_garantisi_ve_muster.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-23_ppap_sunum_indeksi_psw__parca_sunum_garantisi_ve_muster.xlsx
@@ -977,7 +977,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-23&amp;C&amp;"Arial,Regular"&amp;11PPAP Sunum İndeksi, PSW / Parça Sunum Garantisi ve Müşteri Onay Takip Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Mevcut sunum/onay takibi korundu; tekrar sunumun onay veya otomatik izin uzatması sayılmayacağı belirtildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ed8434c98b4983"/>
   <x:tableParts count="1">
@@ -1387,7 +1388,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-23&amp;C&amp;"Arial,Regular"&amp;11PPAP Sunum İndeksi, PSW / Parça Sunum Garantisi ve Müşteri Onay Takip Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Mevcut sunum/onay takibi korundu; tekrar sunumun onay veya otomatik izin uzatması sayılmayacağı belirtildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re92db75cc5c049a7"/>
   <x:tableParts count="1">
@@ -1744,7 +1746,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-23&amp;C&amp;"Arial,Regular"&amp;11PPAP Sunum İndeksi, PSW / Parça Sunum Garantisi ve Müşteri Onay Takip Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Mevcut sunum/onay takibi korundu; tekrar sunumun onay veya otomatik izin uzatması sayılmayacağı belirtildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5582b9074a8649a7"/>
   <x:tableParts count="1">
